--- a/data/sites/hr/Learning and Development/compliance-training-completion-tracker.xlsx
+++ b/data/sites/hr/Learning and Development/compliance-training-completion-tracker.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Compliance Training Completion Tracker</t>
+          <t>Compliance Training Completion Tracker - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,129 +651,2525 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 1 (Executive Summary &amp; Scope) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Code of conduct and anti-harassment training is required annually for all employees. Secondary control 1.2: Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Enrolled</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Completion %</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>92%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>92%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 10 (Cross-Functional Dependencies) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Managers must complete an additional manager-specific compliance module. Secondary control 10.2: Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 11 (Continuous Improvement Roadmap) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Departments below 90% completion are flagged two weeks before the deadline. Secondary control 11.2: Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: Completion data feeds the quarterly compliance report to the audit committee. Secondary control 12.2: Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 2 (Architecture &amp; Process Flow) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Managers must complete an additional manager-specific compliance module. Secondary control 2.2: Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 3 (Governance Standards &amp; Controls) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Departments below 90% completion are flagged two weeks before the deadline. Secondary control 3.2: Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 4 (Operational KPIs &amp; Benchmarks) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: Completion data feeds the quarterly compliance report to the audit committee. Secondary control 4.2: Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 5 (Roles, Responsibilities &amp; RACI) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Code of conduct and anti-harassment training is required annually for all employees. Secondary control 5.2: Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 6 (Standard Operating Procedures) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Managers must complete an additional manager-specific compliance module. Secondary control 6.2: Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 7 (Risk Register &amp; Mitigations) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Departments below 90% completion are flagged two weeks before the deadline. Secondary control 7.2: Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Departments below 90% completion are flagged two weeks before the deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 8 (Quality Assurance &amp; Audits) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: Completion data feeds the quarterly compliance report to the audit committee. Secondary control 8.2: Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Completion data feeds the quarterly compliance report to the audit committee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Training Completion Tracker - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Learning and Development | Owner: Alicia Gomez  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks completion status of mandatory compliance training modules by department against the annual deadline. Section 9 (Exception Handling &amp; Escalations) applies to Learning and Development within HR Knowledge Hub and is maintained by Alicia Gomez. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Code of conduct and anti-harassment training is required annually for all employees. Secondary control 9.2: Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Enrolled</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Completion %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Code of conduct and anti-harassment training is required annually for all employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Managers must complete an additional manager-specific compliance module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Alicia Gomez under Learning and Development governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>